--- a/data/trans_orig/P16A06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A06-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28122</t>
+          <t>28195</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52745</t>
+          <t>52752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76669</t>
+          <t>74228</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113985</t>
+          <t>111939</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109072</t>
+          <t>109743</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>151784</t>
+          <t>155001</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>978978</t>
+          <t>978971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1003601</t>
+          <t>1003528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1201128</t>
+          <t>1203174</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1238444</t>
+          <t>1240885</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2195051</t>
+          <t>2191834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2237763</t>
+          <t>2237092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31458</t>
+          <t>31765</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27057</t>
+          <t>28481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51848</t>
+          <t>53136</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44274</t>
+          <t>46345</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77003</t>
+          <t>77891</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1660936</t>
+          <t>1660629</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1680043</t>
+          <t>1679574</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1535825</t>
+          <t>1534537</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1560616</t>
+          <t>1559192</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3203064</t>
+          <t>3202176</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3235793</t>
+          <t>3233722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12361</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22921</t>
+          <t>23819</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539047</t>
+          <t>540054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549438</t>
+          <t>549518</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>459550</t>
+          <t>459731</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>472503</t>
+          <t>472334</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1004899</t>
+          <t>1004001</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1019975</t>
+          <t>1020032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50520</t>
+          <t>50187</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80965</t>
+          <t>82874</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116772</t>
+          <t>118361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164191</t>
+          <t>165057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>180172</t>
+          <t>176275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235616</t>
+          <t>233535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3194560</t>
+          <t>3192651</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3225005</t>
+          <t>3225338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3215006</t>
+          <t>3214140</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3262425</t>
+          <t>3260836</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6419106</t>
+          <t>6421187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6474550</t>
+          <t>6478447</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17674</t>
+          <t>17160</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39391</t>
+          <t>38021</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114905</t>
+          <t>114945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>160952</t>
+          <t>158928</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134457</t>
+          <t>136621</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>185868</t>
+          <t>191040</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>931199</t>
+          <t>932569</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>952916</t>
+          <t>953430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1171639</t>
+          <t>1173663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1217686</t>
+          <t>1217646</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2117313</t>
+          <t>2112141</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2168724</t>
+          <t>2166560</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23447</t>
+          <t>24224</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49034</t>
+          <t>50677</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59305</t>
+          <t>58956</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94799</t>
+          <t>96636</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88769</t>
+          <t>90431</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131653</t>
+          <t>130854</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1910988</t>
+          <t>1909345</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1936575</t>
+          <t>1935798</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1656036</t>
+          <t>1654199</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1691530</t>
+          <t>1691879</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3579204</t>
+          <t>3580003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3622088</t>
+          <t>3620426</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18563</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23043</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12827</t>
+          <t>12079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37874</t>
+          <t>35184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>461769</t>
+          <t>461253</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477125</t>
+          <t>477119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>434611</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>451252</t>
+          <t>451706</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>900112</t>
+          <t>902802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>925159</t>
+          <t>925907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52435</t>
+          <t>51552</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89564</t>
+          <t>88543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>193116</t>
+          <t>190936</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>252950</t>
+          <t>253363</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>254893</t>
+          <t>257603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>326812</t>
+          <t>326539</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3321380</t>
+          <t>3322401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3358509</t>
+          <t>3359392</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3288130</t>
+          <t>3287717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3347964</t>
+          <t>3350144</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6625212</t>
+          <t>6625485</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6697131</t>
+          <t>6694421</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31606</t>
+          <t>31976</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57888</t>
+          <t>59538</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128631</t>
+          <t>127975</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>174095</t>
+          <t>174563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>169036</t>
+          <t>168782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>221797</t>
+          <t>221114</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>696459</t>
+          <t>694809</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>722741</t>
+          <t>722371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>820565</t>
+          <t>820097</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>866029</t>
+          <t>866685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1527210</t>
+          <t>1527893</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1579971</t>
+          <t>1580225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23813</t>
+          <t>23630</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47835</t>
+          <t>49998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76954</t>
+          <t>77882</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118269</t>
+          <t>119611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109612</t>
+          <t>107077</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154018</t>
+          <t>154900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2028550</t>
+          <t>2026387</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2052572</t>
+          <t>2052755</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1870031</t>
+          <t>1868689</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1911346</t>
+          <t>1910418</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3910667</t>
+          <t>3909785</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3955073</t>
+          <t>3957608</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19715</t>
+          <t>19412</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28595</t>
+          <t>31089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19359</t>
+          <t>20304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42329</t>
+          <t>43175</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527171</t>
+          <t>527474</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542023</t>
+          <t>542180</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>520545</t>
+          <t>518051</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>538592</t>
+          <t>537147</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1053698</t>
+          <t>1052852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1076668</t>
+          <t>1075723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71975</t>
+          <t>71012</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108105</t>
+          <t>107619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>236084</t>
+          <t>236514</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>301009</t>
+          <t>299490</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>317135</t>
+          <t>316844</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>391131</t>
+          <t>394373</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3269513</t>
+          <t>3269999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3305643</t>
+          <t>3306606</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3231091</t>
+          <t>3232610</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3296016</t>
+          <t>3295586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6518587</t>
+          <t>6515345</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6592583</t>
+          <t>6592874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48566</t>
+          <t>47674</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73279</t>
+          <t>72181</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>150606</t>
+          <t>149768</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>190030</t>
+          <t>187418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208011</t>
+          <t>209033</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>252532</t>
+          <t>253931</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440173</t>
+          <t>441271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>464886</t>
+          <t>465778</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>561541</t>
+          <t>564153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>600965</t>
+          <t>601803</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1012491</t>
+          <t>1011092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1057012</t>
+          <t>1055990</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,48%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56972</t>
+          <t>57230</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105267</t>
+          <t>104562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>109572</t>
+          <t>115077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>182374</t>
+          <t>182712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>192705</t>
+          <t>186350</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>275233</t>
+          <t>271032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2185060</t>
+          <t>2185765</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2233355</t>
+          <t>2233097</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2054771</t>
+          <t>2054433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2127573</t>
+          <t>2122068</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4252239</t>
+          <t>4256440</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4334767</t>
+          <t>4341122</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17454</t>
+          <t>17669</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37653</t>
+          <t>38303</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28362</t>
+          <t>28518</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47618</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50339</t>
+          <t>51162</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78036</t>
+          <t>78866</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608970</t>
+          <t>608320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629169</t>
+          <t>628954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>612685</t>
+          <t>612378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>631941</t>
+          <t>631785</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1228890</t>
+          <t>1228060</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1256587</t>
+          <t>1255764</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>126313</t>
+          <t>130108</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>195545</t>
+          <t>196592</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>301155</t>
+          <t>292216</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>399897</t>
+          <t>399838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>459204</t>
+          <t>460161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>578687</t>
+          <t>578054</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3254857</t>
+          <t>3253810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3324089</t>
+          <t>3320294</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,17 +6714,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3289689</t>
+          <t>3289690</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3249121</t>
+          <t>3249181</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3347863</t>
+          <t>3356803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6520734</t>
+          <t>6521367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6640217</t>
+          <t>6639260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649018</t>
+          <t>3649019</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649018</t>
+          <t>3649019</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649018</t>
+          <t>3649019</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">

--- a/data/trans_orig/P16A06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A06-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28195</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52752</t>
+          <t>52347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74228</t>
+          <t>75462</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111939</t>
+          <t>114004</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109743</t>
+          <t>109250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>155001</t>
+          <t>153664</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>978971</t>
+          <t>979376</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1003528</t>
+          <t>1002727</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1203174</t>
+          <t>1201109</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1240885</t>
+          <t>1239651</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2191834</t>
+          <t>2193171</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2237092</t>
+          <t>2237585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31765</t>
+          <t>31307</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28481</t>
+          <t>28008</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53136</t>
+          <t>55311</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46345</t>
+          <t>44965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77891</t>
+          <t>78227</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1660629</t>
+          <t>1661087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1679574</t>
+          <t>1679969</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1534537</t>
+          <t>1532362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1559192</t>
+          <t>1559665</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3202176</t>
+          <t>3201840</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3233722</t>
+          <t>3235102</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>17865</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23819</t>
+          <t>23186</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540054</t>
+          <t>539906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549518</t>
+          <t>549363</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>459731</t>
+          <t>458547</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>472334</t>
+          <t>472385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1004001</t>
+          <t>1004634</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1020032</t>
+          <t>1019785</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50187</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82874</t>
+          <t>83533</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118361</t>
+          <t>118772</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165057</t>
+          <t>165490</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176275</t>
+          <t>180315</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>233535</t>
+          <t>234048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3192651</t>
+          <t>3191992</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3225338</t>
+          <t>3224183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3214140</t>
+          <t>3213707</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3260836</t>
+          <t>3260425</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6421187</t>
+          <t>6420674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6478447</t>
+          <t>6474407</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17160</t>
+          <t>16710</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38021</t>
+          <t>38165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114945</t>
+          <t>114093</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158928</t>
+          <t>159234</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136621</t>
+          <t>135604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191040</t>
+          <t>186634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>932569</t>
+          <t>932425</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>953430</t>
+          <t>953880</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1173663</t>
+          <t>1173357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1217646</t>
+          <t>1218498</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2112141</t>
+          <t>2116547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2166560</t>
+          <t>2167577</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24224</t>
+          <t>22561</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50677</t>
+          <t>46649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58956</t>
+          <t>58705</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96636</t>
+          <t>94248</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90431</t>
+          <t>88660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130854</t>
+          <t>130704</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1909345</t>
+          <t>1913373</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1935798</t>
+          <t>1937461</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1654199</t>
+          <t>1656587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1691879</t>
+          <t>1692130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3580003</t>
+          <t>3580153</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3620426</t>
+          <t>3622197</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>19570</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23072</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>12267</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35184</t>
+          <t>34010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>461253</t>
+          <t>460762</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477119</t>
+          <t>477199</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>434582</t>
+          <t>435132</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>451706</t>
+          <t>451722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>902802</t>
+          <t>903976</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>925907</t>
+          <t>925719</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51552</t>
+          <t>51928</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88543</t>
+          <t>87894</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>190936</t>
+          <t>193360</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>253363</t>
+          <t>253467</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>257603</t>
+          <t>255695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>326539</t>
+          <t>326028</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3322401</t>
+          <t>3323050</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3359392</t>
+          <t>3359016</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3287717</t>
+          <t>3287613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3350144</t>
+          <t>3347720</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6625485</t>
+          <t>6625996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6694421</t>
+          <t>6696329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31976</t>
+          <t>33429</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59538</t>
+          <t>59657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>127975</t>
+          <t>127427</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>174563</t>
+          <t>175232</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168782</t>
+          <t>167591</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>221114</t>
+          <t>223673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>694809</t>
+          <t>694690</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>722371</t>
+          <t>720918</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>820097</t>
+          <t>819428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>866685</t>
+          <t>867233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1527893</t>
+          <t>1525334</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1580225</t>
+          <t>1581416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23630</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49998</t>
+          <t>47806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77882</t>
+          <t>78013</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>119611</t>
+          <t>117676</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>109124</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154900</t>
+          <t>160458</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026387</t>
+          <t>2028579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2052755</t>
+          <t>2052185</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1868689</t>
+          <t>1870624</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1910418</t>
+          <t>1910287</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3909785</t>
+          <t>3904227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3957608</t>
+          <t>3955561</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11993</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31089</t>
+          <t>29217</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43175</t>
+          <t>42472</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527474</t>
+          <t>526991</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542180</t>
+          <t>542070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>518051</t>
+          <t>519923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537147</t>
+          <t>538332</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1052852</t>
+          <t>1053555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1075723</t>
+          <t>1076466</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71012</t>
+          <t>70171</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107619</t>
+          <t>108003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>236514</t>
+          <t>232863</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>299490</t>
+          <t>301597</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>316844</t>
+          <t>321088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>394373</t>
+          <t>394299</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3269999</t>
+          <t>3269615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3306606</t>
+          <t>3307447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3232610</t>
+          <t>3230503</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3295586</t>
+          <t>3299237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6515345</t>
+          <t>6515419</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6592874</t>
+          <t>6588630</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>60131</t>
+          <t>63293</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47674</t>
+          <t>50415</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72181</t>
+          <t>77046</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>168449</t>
+          <t>177500</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>149768</t>
+          <t>161085</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>187418</t>
+          <t>196238</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>228579</t>
+          <t>240793</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>209033</t>
+          <t>219179</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>253931</t>
+          <t>263688</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>453321</t>
+          <t>513754</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441271</t>
+          <t>500001</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465778</t>
+          <t>526632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>583122</t>
+          <t>641570</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>564153</t>
+          <t>622832</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>601803</t>
+          <t>657985</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1036444</t>
+          <t>1155324</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1011092</t>
+          <t>1132429</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1055990</t>
+          <t>1176938</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>84,3%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513452</t>
+          <t>577047</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751571</t>
+          <t>819070</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751571</t>
+          <t>819070</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751571</t>
+          <t>819070</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1265023</t>
+          <t>1396117</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265023</t>
+          <t>1396117</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1265023</t>
+          <t>1396117</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81622</t>
+          <t>90828</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57230</t>
+          <t>73510</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104562</t>
+          <t>112124</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>153600</t>
+          <t>167539</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>115077</t>
+          <t>146505</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>182712</t>
+          <t>187648</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>235222</t>
+          <t>258368</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>186350</t>
+          <t>232610</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>271032</t>
+          <t>289687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2208705</t>
+          <t>2139738</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2185765</t>
+          <t>2118442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2233097</t>
+          <t>2157056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2083545</t>
+          <t>2003168</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2054433</t>
+          <t>1983059</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2122068</t>
+          <t>2024202</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4292250</t>
+          <t>4142906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4256440</t>
+          <t>4111587</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4341122</t>
+          <t>4168664</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26030</t>
+          <t>27651</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17669</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38303</t>
+          <t>39136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37280</t>
+          <t>41521</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>31765</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47925</t>
+          <t>52915</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>63310</t>
+          <t>69171</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51162</t>
+          <t>55988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78866</t>
+          <t>85484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>620593</t>
+          <t>683936</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608320</t>
+          <t>672451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628954</t>
+          <t>693577</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>623023</t>
+          <t>692648</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>612378</t>
+          <t>681254</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>631785</t>
+          <t>702404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1243616</t>
+          <t>1376585</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1228060</t>
+          <t>1360272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1255764</t>
+          <t>1389768</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734169</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734169</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734169</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306926</t>
+          <t>1445756</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306926</t>
+          <t>1445756</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306926</t>
+          <t>1445756</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>167783</t>
+          <t>181771</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>130108</t>
+          <t>156142</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>196592</t>
+          <t>208119</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>359329</t>
+          <t>386561</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>292216</t>
+          <t>357138</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>399838</t>
+          <t>416134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>527112</t>
+          <t>568332</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>460161</t>
+          <t>532566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>578054</t>
+          <t>612508</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3282619</t>
+          <t>3337429</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3253810</t>
+          <t>3311081</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3320294</t>
+          <t>3363058</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3289690</t>
+          <t>3337386</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3249181</t>
+          <t>3307813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3356803</t>
+          <t>3366809</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6572309</t>
+          <t>6674815</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6521367</t>
+          <t>6630639</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6639260</t>
+          <t>6710581</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450402</t>
+          <t>3519200</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649019</t>
+          <t>3723947</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649019</t>
+          <t>3723947</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649019</t>
+          <t>3723947</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7099421</t>
+          <t>7243147</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7099421</t>
+          <t>7243147</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7099421</t>
+          <t>7243147</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
